--- a/feedback_forms/029_youth_and_eternity_feedback_form--feedback_forms.xlsx
+++ b/feedback_forms/029_youth_and_eternity_feedback_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,8 +665,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,12 +694,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'17-20',_'label':_'17-20'}</t>
+          <t>17-20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': '17-20', 'label': '17-20'}</t>
+          <t>17-20</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'21-24',_'label':_'21-24'}</t>
+          <t>21-24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': '21-24', 'label': '21-24'}</t>
+          <t>21-24</t>
         </is>
       </c>
     </row>
@@ -728,12 +728,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'25-29',_'label':_'25-29'}</t>
+          <t>25-29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': '25-29', 'label': '25-29'}</t>
+          <t>25-29</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'30-34',_'label':_'30-34'}</t>
+          <t>30-34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': '30-34', 'label': '30-34'}</t>
+          <t>30-34</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'35-39',_'label':_'35-39'}</t>
+          <t>35-39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': '35-39', 'label': '35-39'}</t>
+          <t>35-39</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'40-44',_'label':_'40-44'}</t>
+          <t>40-44</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': '40-44', 'label': '40-44'}</t>
+          <t>40-44</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'45-49',_'label':_'45-49'}</t>
+          <t>45-49</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': '45-49', 'label': '45-49'}</t>
+          <t>45-49</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'50-54',_'label':_'50-54'}</t>
+          <t>50-54</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': '50-54', 'label': '50-54'}</t>
+          <t>50-54</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'55-59',_'label':_'55-59'}</t>
+          <t>55-59</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': '55-59', 'label': '55-59'}</t>
+          <t>55-59</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'60-64',_'label':_'60-64'}</t>
+          <t>60-64</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': '60-64', 'label': '60-64'}</t>
+          <t>60-64</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_65,_'label':_65}</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 65, 'label': 65}</t>
+          <t>65</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'other', 'label': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
